--- a/public/templates/office/Phase5_월간_정기점검_운영보고서.xlsx
+++ b/public/templates/office/Phase5_월간_정기점검_운영보고서.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월간_정기점검보고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_월간_정기점검_결과표" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,12 +28,13 @@
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="001E293B"/>
-      <sz val="16"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="0064748B"/>
+      <b val="1"/>
+      <color rgb="001E293B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -44,11 +45,17 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00334155"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001E293B"/>
       <sz val="9.5"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -57,14 +64,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E293B"/>
-        <bgColor rgb="001E293B"/>
+        <fgColor rgb="001B365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E8F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002563EB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8FAFC"/>
-        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -94,22 +114,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,34 +514,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>월간_정기점검보고</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>[EMP-XLS-P5-07] SyncGuard AI 월간 정기점검 및 SLA 운영보고서 (2026년 10월) — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>엠파시 사업 및 개발 방법론 표준 시트 (주식회사 엠파시)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="10" customHeight="1"/>
-    <row r="4" ht="28" customHeight="1">
+          <t>EKS 컨테이너·RDS pgvector·일배치·보안패치·AI 추론 SLA 월간 종합 헬스체크 리포트 | 발주처: 주식회사 한빛글로벌 | 수행사: 주식회사 엠파시 | 기준일: 2026.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>점검 영역</t>
@@ -516,286 +553,360 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>목표 기준치</t>
+          <t>SLA 목표 기준치</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>실제 점검 결과</t>
+          <t>당월 측정치</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>상태 (정상/주의/경고)</t>
+          <t>판정 상태</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>이상 징후 및 조치 내역</t>
+          <t>세부 점검 결과 및 특이사항</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>점검자</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
+          <t>점검 담당자</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="21" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>서버 인프라</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>웹/WAS 서버 평균 CPU 사용률</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>70.0 % 이하</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>28.4 %</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>정상</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>피크 시간대 최대 45%로 안정적</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>인프라팀</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>서버 인프라</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>웹/WAS 서버 메모리 점유율</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>80.0 % 이하</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>62.1 %</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>정상</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>JVM 힙 메모리 누수 없음</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>인프라팀</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
+          <t>컨테이너 인프라</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>AWS EKS PRD 노드(m6i.xlarge×4) 평균 CPU 사용률</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>70.0% 이하</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>31.4%</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>정상 (양호)</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>피크 시간대(14:00~16:00) 최대 52.0%로 안정 유지</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>강동현 수석</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>컨테이너 인프라</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>syncguard-ai-worker 파드 메모리 점유율</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>80.0% 이하</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>54.2%</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>정상 (양호)</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>스트리밍 청크 패치 후 메모리 스파이크 0건</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>김태호 책임</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="21" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>데이터베이스</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>PostgreSQL 17 스토리지 사용량</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>75.0 % 이하</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>41.8 %</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>정상</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>잔여 디스크 580 GB 확보</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>DBA</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>RDS PostgreSQL 16 (Multi-AZ) 스토리지 사용률</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>75.0% 이하</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>정상 (양호)</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>할당 1TB 중 385GB 사용, 월별 파티션 자동 생성 완료</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>조현우 선임</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>데이터베이스</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>DB 활성 커넥션 풀 사용률</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>60.0 % 이하</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>35.0 %</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>정상</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>HikariCP 커넥션 안정 유지</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>DBA</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>pgvector HNSW 인덱스 검색 평균 응답시간</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>500ms 이내</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>142ms</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>정상 (우수)</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>48,500개 법령 청크 대상 하이브리드 RRF 검색 고속 유지</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>조현우 선임</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="21" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>백업 및 DR</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>일일 자동 백업 정상 수행 여부</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>100.0 % 성공</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>30일 100% 성공</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>정상</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>오프라인 스토리지 이중 소산 완료</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>인프라팀</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>보안 및 패치</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>OS 및 미들웨어 보안 취약점 패치</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>최신 보안 권고</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>최신 패치 완료</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>정상</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>CVE 취약점 점검 양호</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>보안팀</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
+          <t>기간계 일배치</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>02:00 ProductLab 전성분 마스터 일배치 성공률</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>정상 (완벽)</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>31일 중 31회 전수 성공 (평균 소요시간 2분 48초)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>오정훈 차장</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>AI 심의 품질</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>주간 골든셋(58문항) 자동 회귀 테스트 정밀도</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>95.0% 이상</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>96.6%</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>정상 (우수)</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Precision 96.6%, Recall 98.2%로 환각·오탐 통제</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>김태호 책임</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="21" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>서비스 SLA</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>월간 시스템 가용성(Uptime) 달성률</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>99.90 % 이상</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>99.98 %</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>정상</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>월간 총 가동률 99.98% 달성</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>운영PL</t>
+          <t>AI 응답 SLA</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>단건 홍보문안·이미지 3단계 AI 심의 평균 소요시간</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>15.0초 이내</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>8.1초</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>정상 (우수)</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>95%ile 응답시간 12.4초로 목표 SLA 완벽 충족</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>김태호 책임</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="21" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>보안 및 백업</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>RDS 일일 자동 스냅샷 및 S3 버전 백업 성공률</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>정상 (완벽)</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>35일 보존 정책 정상 작동, 보안 취약점(CVE) 0건</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>오승민 수석</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>종합 가용성</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>월간 서비스 종합 가동률 (Uptime SLA)</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>99.90% 이상</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>99.99%</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>최종 적격</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>월간 계획 외 중단(Unplanned Downtime) 0분 달성</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>박진우 수석</t>
         </is>
       </c>
     </row>

--- a/public/templates/office/Phase5_월간_정기점검_운영보고서.xlsx
+++ b/public/templates/office/Phase5_월간_정기점검_운영보고서.xlsx
@@ -529,7 +529,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[EMP-XLS-P5-07] SyncGuard AI 월간 정기점검 및 SLA 운영보고서 (2026년 10월) — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[EMP-XLS-P5-07] SyncFlow AI 월간 정기점검 및 SLA 운영보고서 (2026년 10월) — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>syncguard-ai-worker 파드 메모리 점유율</t>
+          <t>syncflow-ai-worker 파드 메모리 점유율</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>02:00 ProductLab 전성분 마스터 일배치 성공률</t>
+          <t>02:00 PLM-Nexus 자재BOM 마스터 일배치 성공률</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -765,7 +765,7 @@
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>AI 심의 품질</t>
+          <t>AI 검증 품질</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>단건 홍보문안·이미지 3단계 AI 심의 평균 소요시간</t>
+          <t>단건 조달계약조항·이미지 3단계 AI 검증 평균 소요시간</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
